--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -575,15 +575,19 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Gregoire Burgé</t>
+          <t>Retenu : Joël Nguyen</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>E2.txt</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>video_expert_E2.html</t>
@@ -591,7 +595,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_gregoire-burgé.doc</t>
+          <t>guide_editorial_simplifie_joël-nguyen.doc</t>
         </is>
       </c>
     </row>

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -1632,10 +1632,14 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>E22.txt</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>video_expert_E22.html</t>

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Stephanie Oger-Roussel</t>
+          <t>Retenu : Fatoumata Aonon</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_stephanie-oger-roussel.doc</t>
+          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
         </is>
       </c>
     </row>
@@ -1058,32 +1058,32 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E11bis</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>De la prématuration à la maturation. Étapes, sélection, investissement, jalons et accompagnement.</t>
+          <t>La loi PACTE et le concours scientifique (optionnel). Régime de l’agent public (loi Allègre 1999 / loi PACTE 2019) : participer à une société qui valorise ses travaux sans quitter l’établissement. Ce n’est pas un concours de financement. Distinct du pacte d’associés (E17).</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>VIDÉO 7 : VOUS N'ÊTES PAS SEUL(E)</t>
+          <t>VIDÉO 6 : TRANSFERT ET LICENSING</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Fatoumata Aonon</t>
+          <t>Retenu : Soizic Lefeuvre</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1094,24 +1094,24 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E12.html</t>
+          <t>video_expert_E11bis.html</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_soizic-lefeuvre.doc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Ce que fait réellement un incubateur. Coaching, réseau, formation, confrontation, équipe et préparation de la création.</t>
+          <t>De la prématuration à la maturation. Étapes, sélection, investissement, jalons et accompagnement.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1131,35 +1131,39 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Arielle Santé</t>
+          <t>Retenu : Stephanie Oger-Roussel</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>E12.txt</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E13.html</t>
+          <t>video_expert_E12.html</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_stephanie-oger-roussel.doc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>E13bis</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Autre structures (design spot, Fablab, pole de compétitivité,OTT, etc)</t>
+          <t>Ce que fait réellement un incubateur. Coaching, réseau, formation, confrontation, équipe et préparation de la création.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1179,45 +1183,49 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Yoann Montenot</t>
+          <t>Retenu : Arielle Santé</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>E13.txt</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E13bis.html</t>
+          <t>video_expert_E13.html</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_yoann-montenot.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E13bis</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>La chaîne des financements de l’innovation. Prématuration, maturation, aides non dilutives, concours, Bpifrance et financement privé.</t>
+          <t>Autre structures (design spot, Fablab, pole de compétitivité,OTT, etc)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>VIDÉO 8 : FINANCEMENTS, CONCOURS ET TEMPS POUR ENTREPRENDRE</t>
+          <t>VIDÉO 7 : VOUS N'ÊTES PAS SEUL(E)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1227,7 +1235,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Fatoumata Aonon</t>
+          <t>Retenu : Yoann Montenot</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1238,24 +1246,24 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E14.html</t>
+          <t>video_expert_E13bis.html</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
+          <t>guide_editorial_simplifie_yoann-montenot.doc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Comprendre la logique des investisseurs. Dilution, retour attendu, rythme de croissance, gouvernance et compatibilité avec le projet.</t>
+          <t>La chaîne des financements de l’innovation. Prématuration, maturation, aides non dilutives, concours, Bpifrance et financement privé.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1275,7 +1283,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Arielle Santé</t>
+          <t>Retenu : Fatoumata Aonon</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1286,76 +1294,72 @@
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E15.html</t>
+          <t>video_expert_E14.html</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_fatoumata-aonon.doc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cartographier les compétences nécessaires. Complémentarité, recrutement, rôle du CEO, du CSO et du CTO, et critères humains.</t>
+          <t>Comprendre la logique des investisseurs. Dilution, retour attendu, rythme de croissance, gouvernance et compatibilité avec le projet.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>T9</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>VIDÉO 9 : PARTENARIATS ET POSTURE : CONSTRUIRE UNE ÉQUIPE</t>
+          <t>VIDÉO 8 : FINANCEMENTS, CONCOURS ET TEMPS POUR ENTREPRENDRE</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Pascal Corbel</t>
+          <t>Retenu : Arielle Santé</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>RECU</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>E16.txt</t>
-        </is>
-      </c>
+          <t>EN_ATTENTE</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E16.html</t>
+          <t>video_expert_E15.html</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Organiser la relation entre fondateurs. Gouvernance, responsabilités, répartition du pouvoir, parts, pacte et prévention des conflits.</t>
+          <t>Cartographier les compétences nécessaires. Complémentarité, recrutement, rôle du CEO, du CSO et du CTO, et critères humains.</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1375,45 +1379,49 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Antoine Latreille</t>
+          <t>Retenu : Pascal Corbel</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>E16.txt</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E17.html</t>
+          <t>video_expert_E16.html</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
+          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Passer de la preuve scientifique à la valeur pour l’interlocuteur. Adapter le message selon l’utilisateur, le décideur, le partenaire ou l’investisseur.</t>
+          <t>Organiser la relation entre fondateurs. Gouvernance, responsabilités, répartition du pouvoir, parts, pacte et prévention des conflits.</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>VIDÉO 10 : ENRICHIR SON LANGAGE</t>
+          <t>VIDÉO 9 : PARTENARIATS ET POSTURE : CONSTRUIRE UNE ÉQUIPE</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1423,7 +1431,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Arielle Santé</t>
+          <t>Retenu : Antoine Latreille</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1434,24 +1442,24 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E18.html</t>
+          <t>video_expert_E17.html</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_arielle-santé.doc</t>
+          <t>guide_editorial_simplifie_antoine-latreille.doc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>La posture entrepreneuriale s’apprend. Feedback, entraînement, mentorat et évolution de l’identité professionnelle.</t>
+          <t>Passer de la preuve scientifique à la valeur pour l’interlocuteur. Adapter le message selon l’utilisateur, le décideur, le partenaire ou l’investisseur.</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1471,7 +1479,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Pascal Corbel</t>
+          <t>Retenu : Arielle Santé</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1481,49 +1489,49 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>E19.txt</t>
+          <t>E18.txt</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E19.html</t>
+          <t>video_expert_E18.html</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
+          <t>guide_editorial_simplifie_arielle-santé.doc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Concilier recherche et engagement dans l'innovation. Double casquette, gouvernance, impartialité, évolution du métier de chercheur.</t>
+          <t>La posture entrepreneuriale s’apprend. Feedback, entraînement, mentorat et évolution de l’identité professionnelle.</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>VIDÉO 11 : EVOLUTION DANS LE MÉTIER DU CHERCHEUR.EUSE</t>
+          <t>VIDÉO 10 : ENRICHIR SON LANGAGE</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Bernard Yannou</t>
+          <t>Retenu : Pascal Corbel</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1533,29 +1541,29 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>E20.txt</t>
+          <t>E19.txt</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E20.html</t>
+          <t>video_expert_E19.html</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_bernard-yannou.doc</t>
+          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Innover comme processus d’apprentissage. Incertitude, essais, erreurs, pivot et progression plutôt que réussite linéaire ; leviers existants pour dépasser les freins.</t>
+          <t>Concilier recherche et engagement dans l'innovation. Double casquette, gouvernance, impartialité, évolution du métier de chercheur.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1575,7 +1583,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Pascal Corbel</t>
+          <t>Retenu : Bernard Yannou</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1585,39 +1593,39 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>E21.txt</t>
+          <t>E20.txt</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E21.html</t>
+          <t>video_expert_E20.html</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
+          <t>guide_editorial_simplifie_bernard-yannou.doc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Concevoir une collaboration équilibrée. Objectifs partagés, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+          <t>Innover comme processus d’apprentissage. Incertitude, essais, erreurs, pivot et progression plutôt que réussite linéaire ; leviers existants pour dépasser les freins.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>VIDÉO 12 : DISPOSITIFS D’ACCOMPAGNEMENT &amp; COLLAB</t>
+          <t>VIDÉO 11 : EVOLUTION DANS LE MÉTIER DU CHERCHEUR.EUSE</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1627,7 +1635,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Retenu : Rémi Waché</t>
+          <t>Retenu : Pascal Corbel</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1637,67 +1645,119 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>E22.txt</t>
+          <t>E21.txt</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>video_expert_E22.html</t>
+          <t>video_expert_E21.html</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>guide_editorial_simplifie_rémi-waché.doc</t>
+          <t>guide_editorial_simplifie_pascal-corbel.doc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Concevoir une collaboration équilibrée. Objectifs partagés, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>VIDÉO 12 : DISPOSITIFS D’ACCOMPAGNEMENT &amp; COLLAB</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Retenu : Rémi Waché</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>E22.txt</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>video_expert_E22.html</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>guide_editorial_simplifie_rémi-waché.doc</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>E23</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Sécuriser juridiquement la collaboration. Confidentialité, contrats, connaissances antérieures, résultats nouveaux, PI, publication et sortie du partenariat.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>T12</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>VIDÉO 12 : DISPOSITIFS D’ACCOMPAGNEMENT &amp; COLLAB</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Retenu : Eneli Vino</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>RECU</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>E23.txt</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>video_expert_E23.html</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>guide_editorial_simplifie_eneli-vino.doc</t>
         </is>

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -632,10 +632,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>E3.txt</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>video_expert_E3.html</t>
@@ -1336,10 +1340,14 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>E15.txt</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>video_expert_E15.html</t>
@@ -1436,10 +1444,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>EN_ATTENTE</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>RECU</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>E17.txt</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>video_expert_E17.html</t>

--- a/site/videos_expert.xlsx
+++ b/site/videos_expert.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Videos expert" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Videos expert" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
